--- a/output/yearly_benthic_cover_iteration_4_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_4_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.68851905564853</v>
+        <v>45.32854168045368</v>
       </c>
       <c r="M2" t="n">
-        <v>99.36153915906885</v>
+        <v>99.08195649239536</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.95480152314602</v>
+        <v>88.00845403518308</v>
       </c>
       <c r="C3" t="n">
-        <v>45.84316978039418</v>
+        <v>45.95492198521475</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228609380865345</v>
+        <v>2.228662335147913</v>
       </c>
       <c r="E3" t="n">
-        <v>5.653745210489153</v>
+        <v>5.720161667528894</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428697936217816</v>
+        <v>0.7428874450493045</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94415820718586</v>
+        <v>33.98245677856926</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17201050660195</v>
+        <v>34.172822472268</v>
       </c>
       <c r="I3" t="n">
-        <v>6.570472214245779</v>
+        <v>6.518416805061561</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642936210136135</v>
+        <v>4.643046531558152</v>
       </c>
       <c r="K3" t="n">
-        <v>12.045198476854</v>
+        <v>11.99154596481691</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87577265427595</v>
+        <v>48.81954714513065</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7641409115241</v>
+        <v>106.7660150951623</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.04861665607703</v>
+        <v>86.99217646857328</v>
       </c>
       <c r="C4" t="n">
-        <v>42.57576331040509</v>
+        <v>42.56322632705525</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18490689223434</v>
+        <v>2.179182615921423</v>
       </c>
       <c r="E4" t="n">
-        <v>6.45735960390152</v>
+        <v>6.500389292691</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444306266289222</v>
+        <v>0.7444369299159199</v>
       </c>
       <c r="G4" t="n">
-        <v>33.27852150975685</v>
+        <v>33.22799416056196</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24380882493042</v>
+        <v>34.24409877613231</v>
       </c>
       <c r="I4" t="n">
-        <v>5.486897782194208</v>
+        <v>5.443343881376168</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652691416430764</v>
+        <v>4.652730811974498</v>
       </c>
       <c r="K4" t="n">
-        <v>12.95138334392297</v>
+        <v>13.00782353142669</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29034022860957</v>
+        <v>44.24788300804413</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81748688293763</v>
+        <v>99.81893286652608</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.84618361980976</v>
+        <v>85.6868372079123</v>
       </c>
       <c r="C5" t="n">
-        <v>42.22485473267022</v>
+        <v>42.10268372195377</v>
       </c>
       <c r="D5" t="n">
-        <v>2.126010795513919</v>
+        <v>2.115037531383149</v>
       </c>
       <c r="E5" t="n">
-        <v>7.046720310219915</v>
+        <v>7.066404239081788</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457546612842539</v>
+        <v>0.7457528942090711</v>
       </c>
       <c r="G5" t="n">
-        <v>32.38146954451409</v>
+        <v>32.2499152795659</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30471441907568</v>
+        <v>34.30463313361727</v>
       </c>
       <c r="I5" t="n">
-        <v>4.580547256175303</v>
+        <v>4.544138541248441</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660966633026587</v>
+        <v>4.660955588806694</v>
       </c>
       <c r="K5" t="n">
-        <v>14.15381638019025</v>
+        <v>14.31316279208769</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46891505985636</v>
+        <v>43.43294948925362</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84758617271683</v>
+        <v>99.84879600329509</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.45030598262714</v>
+        <v>84.07772709228479</v>
       </c>
       <c r="C6" t="n">
-        <v>41.54026479326281</v>
+        <v>41.19913018156355</v>
       </c>
       <c r="D6" t="n">
-        <v>2.057694641946842</v>
+        <v>2.035950327747868</v>
       </c>
       <c r="E6" t="n">
-        <v>7.457431649984451</v>
+        <v>7.434250799269079</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468799512374948</v>
+        <v>0.7468741780017574</v>
       </c>
       <c r="G6" t="n">
-        <v>31.34093981117569</v>
+        <v>31.04400021702435</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35647775692476</v>
+        <v>34.35621218808084</v>
       </c>
       <c r="I6" t="n">
-        <v>3.82288247612357</v>
+        <v>3.792475769649911</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667999695234343</v>
+        <v>4.667963612510983</v>
       </c>
       <c r="K6" t="n">
-        <v>15.54969401737285</v>
+        <v>15.92227290771522</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78280376558169</v>
+        <v>42.75237084013099</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87276257621735</v>
+        <v>99.87377392940977</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.88790069563443</v>
+        <v>82.33678059551572</v>
       </c>
       <c r="C7" t="n">
-        <v>40.57149666681336</v>
+        <v>40.0468617710587</v>
       </c>
       <c r="D7" t="n">
-        <v>1.98154354649049</v>
+        <v>1.950959138520868</v>
       </c>
       <c r="E7" t="n">
-        <v>7.713084267403338</v>
+        <v>7.651313924993951</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478380380385985</v>
+        <v>0.747830997230552</v>
       </c>
       <c r="G7" t="n">
-        <v>30.18107534411631</v>
+        <v>29.74806167626104</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40054974977553</v>
+        <v>34.40022587260539</v>
       </c>
       <c r="I7" t="n">
-        <v>3.189822012068923</v>
+        <v>3.164445253212968</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673987737741241</v>
+        <v>4.673943732690949</v>
       </c>
       <c r="K7" t="n">
-        <v>17.11209930436558</v>
+        <v>17.66321940448429</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21021284892875</v>
+        <v>42.18457227530008</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89380882010768</v>
+        <v>99.89465345084307</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.60251091357819</v>
+        <v>87.30941458537654</v>
       </c>
       <c r="C8" t="n">
-        <v>42.82441265372275</v>
+        <v>42.35395042872965</v>
       </c>
       <c r="D8" t="n">
-        <v>1.985714011920394</v>
+        <v>1.955207711297029</v>
       </c>
       <c r="E8" t="n">
-        <v>9.506941766916638</v>
+        <v>9.49199466804199</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494119790656987</v>
+        <v>0.7494595369335475</v>
       </c>
       <c r="G8" t="n">
-        <v>30.67247550780915</v>
+        <v>30.24952203862452</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47295103702213</v>
+        <v>34.47513869894318</v>
       </c>
       <c r="I8" t="n">
-        <v>5.531191741683557</v>
+        <v>5.703969825701602</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683824869160617</v>
+        <v>4.684122105834671</v>
       </c>
       <c r="K8" t="n">
-        <v>12.39748908642182</v>
+        <v>12.69058541462346</v>
       </c>
       <c r="L8" t="n">
-        <v>44.59411242848966</v>
+        <v>44.76574497757107</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81601416863424</v>
+        <v>99.81028082092418</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.42463535030848</v>
+        <v>85.20123244092808</v>
       </c>
       <c r="C9" t="n">
-        <v>41.504888777676</v>
+        <v>41.13021984179608</v>
       </c>
       <c r="D9" t="n">
-        <v>1.886542815937326</v>
+        <v>1.859811187310864</v>
       </c>
       <c r="E9" t="n">
-        <v>9.801748171259879</v>
+        <v>9.822564847587948</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507622954363334</v>
+        <v>0.7508558584019753</v>
       </c>
       <c r="G9" t="n">
-        <v>29.1406204362276</v>
+        <v>28.77361784795756</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53506559007133</v>
+        <v>34.53936948649086</v>
       </c>
       <c r="I9" t="n">
-        <v>4.617631694898923</v>
+        <v>4.762164098166529</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692264346477084</v>
+        <v>4.692849115012345</v>
       </c>
       <c r="K9" t="n">
-        <v>14.57536464969152</v>
+        <v>14.79876755907192</v>
       </c>
       <c r="L9" t="n">
-        <v>43.76610235758572</v>
+        <v>43.91256899286252</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84635578495323</v>
+        <v>99.84155639373051</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.08992729384542</v>
+        <v>82.82694457420702</v>
       </c>
       <c r="C10" t="n">
-        <v>39.88630339780073</v>
+        <v>39.49397355483816</v>
       </c>
       <c r="D10" t="n">
-        <v>1.781415178891323</v>
+        <v>1.753462732754451</v>
       </c>
       <c r="E10" t="n">
-        <v>9.897874865454236</v>
+        <v>9.923356788473574</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519230537718115</v>
+        <v>0.7520569633379609</v>
       </c>
       <c r="G10" t="n">
-        <v>27.51675876575023</v>
+        <v>27.12827351891754</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58846047350332</v>
+        <v>34.5946203135462</v>
       </c>
       <c r="I10" t="n">
-        <v>3.853975870400677</v>
+        <v>3.974818236315032</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699519086073821</v>
+        <v>4.700356020862255</v>
       </c>
       <c r="K10" t="n">
-        <v>16.91007270615456</v>
+        <v>17.173055425793</v>
       </c>
       <c r="L10" t="n">
-        <v>43.07535634896418</v>
+        <v>43.20068868330865</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87173245291949</v>
+        <v>99.8677176639398</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.68386595996866</v>
+        <v>80.42821680860786</v>
       </c>
       <c r="C11" t="n">
-        <v>38.07718495643536</v>
+        <v>37.71048032626147</v>
       </c>
       <c r="D11" t="n">
-        <v>1.674283981587219</v>
+        <v>1.647334298992263</v>
       </c>
       <c r="E11" t="n">
-        <v>9.838619555017827</v>
+        <v>9.875562036291161</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529220637250973</v>
+        <v>0.7530908041620322</v>
       </c>
       <c r="G11" t="n">
-        <v>25.86194895642904</v>
+        <v>25.48633318824834</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63441493135447</v>
+        <v>34.64217699145348</v>
       </c>
       <c r="I11" t="n">
-        <v>3.215913573573145</v>
+        <v>3.316901963447878</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705762898281858</v>
+        <v>4.706817526012701</v>
       </c>
       <c r="K11" t="n">
-        <v>19.31613404003134</v>
+        <v>19.57178319139215</v>
       </c>
       <c r="L11" t="n">
-        <v>42.49962611824438</v>
+        <v>42.60732486467099</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89294511471108</v>
+        <v>99.8895883823246</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.21629123102296</v>
+        <v>77.97404452463653</v>
       </c>
       <c r="C12" t="n">
-        <v>36.10685449080975</v>
+        <v>35.76882887197912</v>
       </c>
       <c r="D12" t="n">
-        <v>1.565531853298865</v>
+        <v>1.539915147308362</v>
       </c>
       <c r="E12" t="n">
-        <v>9.646723197242013</v>
+        <v>9.692823550319208</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7537829602692635</v>
+        <v>0.7539817286468681</v>
       </c>
       <c r="G12" t="n">
-        <v>24.18210131909446</v>
+        <v>23.82442382820548</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67401617238612</v>
+        <v>34.68315951775593</v>
       </c>
       <c r="I12" t="n">
-        <v>2.682992227049351</v>
+        <v>2.767354948357752</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711143501682897</v>
+        <v>4.712385804042925</v>
       </c>
       <c r="K12" t="n">
-        <v>21.78370876897704</v>
+        <v>22.02595547536347</v>
       </c>
       <c r="L12" t="n">
-        <v>42.02010580761394</v>
+        <v>42.11307948700608</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91066906740073</v>
+        <v>99.90786383434869</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.70649706764362</v>
+        <v>75.53041511493615</v>
       </c>
       <c r="C13" t="n">
-        <v>34.01098297583768</v>
+        <v>33.75186969871814</v>
       </c>
       <c r="D13" t="n">
-        <v>1.455954139956218</v>
+        <v>1.434036172557142</v>
       </c>
       <c r="E13" t="n">
-        <v>9.344516218626968</v>
+        <v>9.411126622584321</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545257361954947</v>
+        <v>0.7547498742402221</v>
       </c>
       <c r="G13" t="n">
-        <v>22.48950122233953</v>
+        <v>22.18634294213975</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70818386499275</v>
+        <v>34.71849421505022</v>
       </c>
       <c r="I13" t="n">
-        <v>2.238030034310825</v>
+        <v>2.308478574363114</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715785851221842</v>
+        <v>4.717186714001388</v>
       </c>
       <c r="K13" t="n">
-        <v>24.29350293235637</v>
+        <v>24.46958488506383</v>
       </c>
       <c r="L13" t="n">
-        <v>41.62098652994347</v>
+        <v>41.70167444543031</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92547243813752</v>
+        <v>99.92312902921229</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.87745609995591</v>
+        <v>82.7639071604827</v>
       </c>
       <c r="C14" t="n">
-        <v>38.53973132519646</v>
+        <v>38.25680611734322</v>
       </c>
       <c r="D14" t="n">
-        <v>1.457599418932231</v>
+        <v>1.435762507944311</v>
       </c>
       <c r="E14" t="n">
-        <v>11.83936878006898</v>
+        <v>11.9095062916807</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7553783766026031</v>
+        <v>0.755658464582151</v>
       </c>
       <c r="G14" t="n">
-        <v>24.53093599063136</v>
+        <v>24.20193353394836</v>
       </c>
       <c r="H14" t="n">
-        <v>36.76342617097746</v>
+        <v>36.74917138321847</v>
       </c>
       <c r="I14" t="n">
-        <v>2.809632508977007</v>
+        <v>2.98900957547027</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721114853766269</v>
+        <v>4.722865403638443</v>
       </c>
       <c r="K14" t="n">
-        <v>17.12254390004411</v>
+        <v>17.23609283951729</v>
       </c>
       <c r="L14" t="n">
-        <v>44.24417607109255</v>
+        <v>44.40758718836134</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90645129633312</v>
+        <v>99.90048614522185</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.9461309577992</v>
+        <v>82.0601707711245</v>
       </c>
       <c r="C15" t="n">
-        <v>38.0421841614364</v>
+        <v>38.00644009840979</v>
       </c>
       <c r="D15" t="n">
-        <v>1.423068566678758</v>
+        <v>1.409380825753902</v>
       </c>
       <c r="E15" t="n">
-        <v>11.94949026096307</v>
+        <v>12.11406601350589</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7560984834358697</v>
+        <v>0.7564238101648326</v>
       </c>
       <c r="G15" t="n">
-        <v>23.94979269753618</v>
+        <v>23.76506311034957</v>
       </c>
       <c r="H15" t="n">
-        <v>36.79847297032997</v>
+        <v>36.79422411242538</v>
       </c>
       <c r="I15" t="n">
-        <v>2.343592457381171</v>
+        <v>2.493364085394727</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725615521474186</v>
+        <v>4.727648813530203</v>
       </c>
       <c r="K15" t="n">
-        <v>18.05386904220081</v>
+        <v>17.9398292288755</v>
       </c>
       <c r="L15" t="n">
-        <v>43.82590144889123</v>
+        <v>43.97070262895166</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92195465252843</v>
+        <v>99.91697195623695</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.28419078007327</v>
+        <v>79.62010557455837</v>
       </c>
       <c r="C16" t="n">
-        <v>35.742008783302</v>
+        <v>35.95116913062397</v>
       </c>
       <c r="D16" t="n">
-        <v>1.322657145879294</v>
+        <v>1.31830129806033</v>
       </c>
       <c r="E16" t="n">
-        <v>11.43210316163512</v>
+        <v>11.67781125003279</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567198217047286</v>
+        <v>0.7570823826618281</v>
       </c>
       <c r="G16" t="n">
-        <v>22.25990032768024</v>
+        <v>22.22927471012016</v>
       </c>
       <c r="H16" t="n">
-        <v>36.82871281340984</v>
+        <v>36.82625861969909</v>
       </c>
       <c r="I16" t="n">
-        <v>1.954598624109489</v>
+        <v>2.079612422347736</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729498885654554</v>
+        <v>4.731764891636426</v>
       </c>
       <c r="K16" t="n">
-        <v>20.71580921992673</v>
+        <v>20.37989442544165</v>
       </c>
       <c r="L16" t="n">
-        <v>43.47708220628846</v>
+        <v>43.59967633045118</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9349002095172</v>
+        <v>99.9307398865168</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.90355416579725</v>
+        <v>81.63333632174913</v>
       </c>
       <c r="C17" t="n">
-        <v>36.92638287944731</v>
+        <v>37.39644920054057</v>
       </c>
       <c r="D17" t="n">
-        <v>1.323714313153161</v>
+        <v>1.319419575697568</v>
       </c>
       <c r="E17" t="n">
-        <v>12.18086389842543</v>
+        <v>12.56842482098519</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757324649216896</v>
+        <v>0.7577245941952035</v>
       </c>
       <c r="G17" t="n">
-        <v>22.69399436682893</v>
+        <v>22.78260255789562</v>
       </c>
       <c r="H17" t="n">
-        <v>37.27445134548476</v>
+        <v>37.39196867532129</v>
       </c>
       <c r="I17" t="n">
-        <v>1.93992653508247</v>
+        <v>2.077417383934236</v>
       </c>
       <c r="J17" t="n">
-        <v>4.7332790576056</v>
+        <v>4.735778713720022</v>
       </c>
       <c r="K17" t="n">
-        <v>19.09644583420275</v>
+        <v>18.36666367825088</v>
       </c>
       <c r="L17" t="n">
-        <v>43.91255871175305</v>
+        <v>44.16769856576853</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93538742540311</v>
+        <v>99.93081144455999</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.33591085506421</v>
+        <v>79.31059979331751</v>
       </c>
       <c r="C18" t="n">
-        <v>34.65768815787508</v>
+        <v>35.39396521255505</v>
       </c>
       <c r="D18" t="n">
-        <v>1.230666953333145</v>
+        <v>1.236746296393004</v>
       </c>
       <c r="E18" t="n">
-        <v>11.59425865596027</v>
+        <v>12.06964237738897</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7578459673474084</v>
+        <v>0.7582763126560687</v>
       </c>
       <c r="G18" t="n">
-        <v>21.09877382821153</v>
+        <v>21.35507146828148</v>
       </c>
       <c r="H18" t="n">
-        <v>37.30010988876788</v>
+        <v>37.41919471439182</v>
       </c>
       <c r="I18" t="n">
-        <v>1.617718265522686</v>
+        <v>1.732441670105729</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736537295921302</v>
+        <v>4.739226954100429</v>
       </c>
       <c r="K18" t="n">
-        <v>21.66408914493577</v>
+        <v>20.6894002066825</v>
       </c>
       <c r="L18" t="n">
-        <v>43.62433584899242</v>
+        <v>43.85892854231984</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94611315180327</v>
+        <v>99.94229396155738</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.27933434079972</v>
+        <v>78.4932653771009</v>
       </c>
       <c r="C19" t="n">
-        <v>33.83258348106014</v>
+        <v>34.84301893712873</v>
       </c>
       <c r="D19" t="n">
-        <v>1.192319735195141</v>
+        <v>1.20832401601621</v>
       </c>
       <c r="E19" t="n">
-        <v>11.46055501283478</v>
+        <v>12.03302844508041</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7582923040764763</v>
+        <v>0.7587414889308692</v>
       </c>
       <c r="G19" t="n">
-        <v>20.44134227839741</v>
+        <v>20.86429997334498</v>
       </c>
       <c r="H19" t="n">
-        <v>37.32207795320173</v>
+        <v>37.44215009531663</v>
       </c>
       <c r="I19" t="n">
-        <v>1.365420156616205</v>
+        <v>1.44458705259388</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739326900477977</v>
+        <v>4.742134305817933</v>
       </c>
       <c r="K19" t="n">
-        <v>22.72066565920028</v>
+        <v>21.50673462289909</v>
       </c>
       <c r="L19" t="n">
-        <v>43.40126364441537</v>
+        <v>43.60212306024702</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95451278467579</v>
+        <v>99.95187662027485</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.66182806416801</v>
+        <v>76.04504185711248</v>
       </c>
       <c r="C20" t="n">
-        <v>31.424644742291</v>
+        <v>32.61680749402207</v>
       </c>
       <c r="D20" t="n">
-        <v>1.098574195082207</v>
+        <v>1.122178424861957</v>
       </c>
       <c r="E20" t="n">
-        <v>10.74921270885864</v>
+        <v>11.37589531871113</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7586777136661311</v>
+        <v>0.7591420727247178</v>
       </c>
       <c r="G20" t="n">
-        <v>18.83415201226625</v>
+        <v>19.37681198883127</v>
       </c>
       <c r="H20" t="n">
-        <v>37.34104726974587</v>
+        <v>37.46191798563743</v>
       </c>
       <c r="I20" t="n">
-        <v>1.138428454135585</v>
+        <v>1.204458111816491</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74173571041332</v>
+        <v>4.744637954529486</v>
       </c>
       <c r="K20" t="n">
-        <v>25.33817193583199</v>
+        <v>23.95495814288753</v>
       </c>
       <c r="L20" t="n">
-        <v>43.19925498419322</v>
+        <v>43.38810694496279</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96207166231622</v>
+        <v>99.95987258187239</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.94632891327129</v>
+        <v>82.16453055208596</v>
       </c>
       <c r="C21" t="n">
-        <v>35.42354739032307</v>
+        <v>36.44405251318445</v>
       </c>
       <c r="D21" t="n">
-        <v>1.099264416759967</v>
+        <v>1.122949972689498</v>
       </c>
       <c r="E21" t="n">
-        <v>12.8758270578547</v>
+        <v>13.43126835901234</v>
       </c>
       <c r="F21" t="n">
-        <v>0.75915438224869</v>
+        <v>0.7596640168327393</v>
       </c>
       <c r="G21" t="n">
-        <v>20.71155774557666</v>
+        <v>21.15522707977171</v>
       </c>
       <c r="H21" t="n">
-        <v>39.23008067495311</v>
+        <v>39.25276739533996</v>
       </c>
       <c r="I21" t="n">
-        <v>1.525729746823861</v>
+        <v>1.694753623235087</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744714889054313</v>
+        <v>4.747900105204621</v>
       </c>
       <c r="K21" t="n">
-        <v>19.05367108672872</v>
+        <v>17.83546944791406</v>
       </c>
       <c r="L21" t="n">
-        <v>45.47195579794597</v>
+        <v>45.66402506540302</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94917427499774</v>
+        <v>99.94354702650151</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_4_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_4_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.32854168045368</v>
+        <v>45.22237901379605</v>
       </c>
       <c r="M2" t="n">
-        <v>99.08195649239536</v>
+        <v>100.2536890897408</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.00845403518308</v>
+        <v>88.0531431906804</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95492198521475</v>
+        <v>45.92117761219669</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228662335147913</v>
+        <v>2.228802560603981</v>
       </c>
       <c r="E3" t="n">
-        <v>5.720161667528894</v>
+        <v>5.703546093199088</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428874450493045</v>
+        <v>0.7429341868679938</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98245677856926</v>
+        <v>33.97023309600151</v>
       </c>
       <c r="H3" t="n">
-        <v>34.172822472268</v>
+        <v>34.17497259592771</v>
       </c>
       <c r="I3" t="n">
-        <v>6.518416805061561</v>
+        <v>6.589315990155143</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643046531558152</v>
+        <v>4.643338667924962</v>
       </c>
       <c r="K3" t="n">
-        <v>11.99154596481691</v>
+        <v>11.9468568093196</v>
       </c>
       <c r="L3" t="n">
-        <v>48.81954714513065</v>
+        <v>48.89545055982295</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7660150951623</v>
+        <v>106.7634849813392</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.99217646857328</v>
+        <v>87.05966213297815</v>
       </c>
       <c r="C4" t="n">
-        <v>42.56322632705525</v>
+        <v>42.56721765538074</v>
       </c>
       <c r="D4" t="n">
-        <v>2.179182615921423</v>
+        <v>2.180543635768847</v>
       </c>
       <c r="E4" t="n">
-        <v>6.500389292691</v>
+        <v>6.49716156597137</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444369299159199</v>
+        <v>0.7444994423491016</v>
       </c>
       <c r="G4" t="n">
-        <v>33.22799416056196</v>
+        <v>33.23469601676931</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24409877613231</v>
+        <v>34.24697434805867</v>
       </c>
       <c r="I4" t="n">
-        <v>5.443343881376168</v>
+        <v>5.502665609378965</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652730811974498</v>
+        <v>4.653121514681885</v>
       </c>
       <c r="K4" t="n">
-        <v>13.00782353142669</v>
+        <v>12.94033786702187</v>
       </c>
       <c r="L4" t="n">
-        <v>44.24788300804413</v>
+        <v>44.30940792231529</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81893286652608</v>
+        <v>99.81696344471789</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.6868372079123</v>
+        <v>85.90743664267765</v>
       </c>
       <c r="C5" t="n">
-        <v>42.10268372195377</v>
+        <v>42.26893428297191</v>
       </c>
       <c r="D5" t="n">
-        <v>2.115037531383149</v>
+        <v>2.124377527451109</v>
       </c>
       <c r="E5" t="n">
-        <v>7.066404239081788</v>
+        <v>7.095430028747302</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457528942090711</v>
+        <v>0.7458264629024519</v>
       </c>
       <c r="G5" t="n">
-        <v>32.2499152795659</v>
+        <v>32.37864181736467</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30463313361727</v>
+        <v>34.30801729351279</v>
       </c>
       <c r="I5" t="n">
-        <v>4.544138541248441</v>
+        <v>4.593728119559004</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660955588806694</v>
+        <v>4.661415393140325</v>
       </c>
       <c r="K5" t="n">
-        <v>14.31316279208769</v>
+        <v>14.09256335732234</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43294948925362</v>
+        <v>43.48565053722303</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84879600329509</v>
+        <v>99.84714817751728</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.07772709228479</v>
+        <v>84.43542984595204</v>
       </c>
       <c r="C6" t="n">
-        <v>41.19913018156355</v>
+        <v>41.51028683412312</v>
       </c>
       <c r="D6" t="n">
-        <v>2.035950327747868</v>
+        <v>2.052305656011632</v>
       </c>
       <c r="E6" t="n">
-        <v>7.434250799269079</v>
+        <v>7.493693131892337</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468741780017574</v>
+        <v>0.7469553036656649</v>
       </c>
       <c r="G6" t="n">
-        <v>31.04400021702435</v>
+        <v>31.28016036560224</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35621218808084</v>
+        <v>34.35994396862058</v>
       </c>
       <c r="I6" t="n">
-        <v>3.792475769649911</v>
+        <v>3.833900772249177</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667963612510983</v>
+        <v>4.668470647910405</v>
       </c>
       <c r="K6" t="n">
-        <v>15.92227290771522</v>
+        <v>15.56457015404795</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75237084013099</v>
+        <v>42.79753945295229</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87377392940977</v>
+        <v>99.87239644112336</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.33678059551572</v>
+        <v>82.77142891575048</v>
       </c>
       <c r="C7" t="n">
-        <v>40.0468617710587</v>
+        <v>40.44159974533824</v>
       </c>
       <c r="D7" t="n">
-        <v>1.950959138520868</v>
+        <v>1.971193584638768</v>
       </c>
       <c r="E7" t="n">
-        <v>7.651313924993951</v>
+        <v>7.730696518817439</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747830997230552</v>
+        <v>0.74791760629362</v>
       </c>
       <c r="G7" t="n">
-        <v>29.74806167626104</v>
+        <v>30.04389295450908</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40022587260539</v>
+        <v>34.40420988950653</v>
       </c>
       <c r="I7" t="n">
-        <v>3.164445253212968</v>
+        <v>3.199033322649924</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673943732690949</v>
+        <v>4.674485039335125</v>
       </c>
       <c r="K7" t="n">
-        <v>17.66321940448429</v>
+        <v>17.22857108424953</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18457227530008</v>
+        <v>42.22333192673864</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89465345084307</v>
+        <v>99.8935027563264</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.30941458537654</v>
+        <v>87.5661817519518</v>
       </c>
       <c r="C8" t="n">
-        <v>42.35395042872965</v>
+        <v>42.73866482417882</v>
       </c>
       <c r="D8" t="n">
-        <v>1.955207711297029</v>
+        <v>1.975376997691951</v>
       </c>
       <c r="E8" t="n">
-        <v>9.49199466804199</v>
+        <v>9.556654631610597</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494595369335475</v>
+        <v>0.7495048924441314</v>
       </c>
       <c r="G8" t="n">
-        <v>30.24952203862452</v>
+        <v>30.54783146304223</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47513869894318</v>
+        <v>34.47722505243005</v>
       </c>
       <c r="I8" t="n">
-        <v>5.703969825701602</v>
+        <v>5.57518313695702</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684122105834671</v>
+        <v>4.684405577775822</v>
       </c>
       <c r="K8" t="n">
-        <v>12.69058541462346</v>
+        <v>12.43381824804819</v>
       </c>
       <c r="L8" t="n">
-        <v>44.76574497757107</v>
+        <v>44.64207105683973</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81028082092418</v>
+        <v>99.81455412906675</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.20123244092808</v>
+        <v>85.44574003542776</v>
       </c>
       <c r="C9" t="n">
-        <v>41.13021984179608</v>
+        <v>41.48325725950889</v>
       </c>
       <c r="D9" t="n">
-        <v>1.859811187310864</v>
+        <v>1.879242028053421</v>
       </c>
       <c r="E9" t="n">
-        <v>9.822564847587948</v>
+        <v>9.867301296610526</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508558584019753</v>
+        <v>0.7508657997492119</v>
       </c>
       <c r="G9" t="n">
-        <v>28.77361784795756</v>
+        <v>29.06117101612309</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53936948649086</v>
+        <v>34.53982678846375</v>
       </c>
       <c r="I9" t="n">
-        <v>4.762164098166529</v>
+        <v>4.654421857995183</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692849115012345</v>
+        <v>4.692911248432575</v>
       </c>
       <c r="K9" t="n">
-        <v>14.79876755907192</v>
+        <v>14.55425996457225</v>
       </c>
       <c r="L9" t="n">
-        <v>43.91256899286252</v>
+        <v>43.80761657767005</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84155639373051</v>
+        <v>99.84513380175119</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.82694457420702</v>
+        <v>83.15480227376193</v>
       </c>
       <c r="C10" t="n">
-        <v>39.49397355483816</v>
+        <v>39.91408985914754</v>
       </c>
       <c r="D10" t="n">
-        <v>1.753462732754451</v>
+        <v>1.776503834668762</v>
       </c>
       <c r="E10" t="n">
-        <v>9.923356788473574</v>
+        <v>9.975309913390872</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520569633379609</v>
+        <v>0.7520350675755333</v>
       </c>
       <c r="G10" t="n">
-        <v>27.12827351891754</v>
+        <v>27.47239630628343</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5946203135462</v>
+        <v>34.59361310847454</v>
       </c>
       <c r="I10" t="n">
-        <v>3.974818236315032</v>
+        <v>3.884724871021712</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700356020862255</v>
+        <v>4.700219172347084</v>
       </c>
       <c r="K10" t="n">
-        <v>17.173055425793</v>
+        <v>16.84519772623807</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20068868330865</v>
+        <v>43.11142291855897</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8677176639398</v>
+        <v>99.87071050394459</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.42821680860786</v>
+        <v>80.73835518246813</v>
       </c>
       <c r="C11" t="n">
-        <v>37.71048032626147</v>
+        <v>38.09934315160002</v>
       </c>
       <c r="D11" t="n">
-        <v>1.647334298992263</v>
+        <v>1.66929157494488</v>
       </c>
       <c r="E11" t="n">
-        <v>9.875562036291161</v>
+        <v>9.913565740691761</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530908041620322</v>
+        <v>0.7530415282137797</v>
       </c>
       <c r="G11" t="n">
-        <v>25.48633318824834</v>
+        <v>25.81443327206578</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64217699145348</v>
+        <v>34.63991029783387</v>
       </c>
       <c r="I11" t="n">
-        <v>3.316901963447878</v>
+        <v>3.241603217381936</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706817526012701</v>
+        <v>4.706509551336124</v>
       </c>
       <c r="K11" t="n">
-        <v>19.57178319139215</v>
+        <v>19.26164481753187</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60732486467099</v>
+        <v>42.53110300667304</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8895883823246</v>
+        <v>99.89209097580493</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.97404452463653</v>
+        <v>78.35235094684666</v>
       </c>
       <c r="C12" t="n">
-        <v>35.76882887197912</v>
+        <v>36.21455054937556</v>
       </c>
       <c r="D12" t="n">
-        <v>1.539915147308362</v>
+        <v>1.5645862866204</v>
       </c>
       <c r="E12" t="n">
-        <v>9.692823550319208</v>
+        <v>9.742484092938664</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539817286468681</v>
+        <v>0.7539079385773378</v>
       </c>
       <c r="G12" t="n">
-        <v>23.82442382820548</v>
+        <v>24.19523880702815</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68315951775593</v>
+        <v>34.67976517455755</v>
       </c>
       <c r="I12" t="n">
-        <v>2.767354948357752</v>
+        <v>2.704444031016192</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712385804042925</v>
+        <v>4.711924616108362</v>
       </c>
       <c r="K12" t="n">
-        <v>22.02595547536347</v>
+        <v>21.64764905315334</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11307948700608</v>
+        <v>42.04775586365494</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90786383434869</v>
+        <v>99.90995546618385</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.53041511493615</v>
+        <v>75.92285169366713</v>
       </c>
       <c r="C13" t="n">
-        <v>33.75186969871814</v>
+        <v>34.20233509851506</v>
       </c>
       <c r="D13" t="n">
-        <v>1.434036172557142</v>
+        <v>1.458961887523358</v>
       </c>
       <c r="E13" t="n">
-        <v>9.411126622584321</v>
+        <v>9.460763361714333</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547498742402221</v>
+        <v>0.7546546473199387</v>
       </c>
       <c r="G13" t="n">
-        <v>22.18634294213975</v>
+        <v>22.56183093310256</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71849421505022</v>
+        <v>34.71411377671719</v>
       </c>
       <c r="I13" t="n">
-        <v>2.308478574363114</v>
+        <v>2.255935541540124</v>
       </c>
       <c r="J13" t="n">
-        <v>4.717186714001388</v>
+        <v>4.716591545749618</v>
       </c>
       <c r="K13" t="n">
-        <v>24.46958488506383</v>
+        <v>24.07714830633287</v>
       </c>
       <c r="L13" t="n">
-        <v>41.70167444543031</v>
+        <v>41.64539314984607</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92312902921229</v>
+        <v>99.92487655469401</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.7639071604827</v>
+        <v>83.10232541161363</v>
       </c>
       <c r="C14" t="n">
-        <v>38.25680611734322</v>
+        <v>38.62874927602885</v>
       </c>
       <c r="D14" t="n">
-        <v>1.435762507944311</v>
+        <v>1.460717525193518</v>
       </c>
       <c r="E14" t="n">
-        <v>11.9095062916807</v>
+        <v>11.92106241408669</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755658464582151</v>
+        <v>0.7555627588601556</v>
       </c>
       <c r="G14" t="n">
-        <v>24.20193353394836</v>
+        <v>24.53789037431945</v>
       </c>
       <c r="H14" t="n">
-        <v>36.74917138321847</v>
+        <v>36.70479663320021</v>
       </c>
       <c r="I14" t="n">
-        <v>2.98900957547027</v>
+        <v>3.000028463077632</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722865403638443</v>
+        <v>4.722267242875973</v>
       </c>
       <c r="K14" t="n">
-        <v>17.23609283951729</v>
+        <v>16.89767458838638</v>
       </c>
       <c r="L14" t="n">
-        <v>44.40758718836134</v>
+        <v>44.37369537804322</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90048614522185</v>
+        <v>99.90011924245844</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.0601707711245</v>
+        <v>82.34469107329227</v>
       </c>
       <c r="C15" t="n">
-        <v>38.00644009840979</v>
+        <v>38.33426935401036</v>
       </c>
       <c r="D15" t="n">
-        <v>1.409380825753902</v>
+        <v>1.432982615995806</v>
       </c>
       <c r="E15" t="n">
-        <v>12.11406601350589</v>
+        <v>12.11180775915226</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564238101648326</v>
+        <v>0.7563281748823597</v>
       </c>
       <c r="G15" t="n">
-        <v>23.76506311034957</v>
+        <v>24.07198498898836</v>
       </c>
       <c r="H15" t="n">
-        <v>36.79422411242538</v>
+        <v>36.74198009560005</v>
       </c>
       <c r="I15" t="n">
-        <v>2.493364085394727</v>
+        <v>2.502556345658683</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727648813530203</v>
+        <v>4.727051093014749</v>
       </c>
       <c r="K15" t="n">
-        <v>17.9398292288755</v>
+        <v>17.65530892670773</v>
       </c>
       <c r="L15" t="n">
-        <v>43.97070262895166</v>
+        <v>43.92708759530754</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91697195623695</v>
+        <v>99.91666587602563</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.62010557455837</v>
+        <v>79.85687366839157</v>
       </c>
       <c r="C16" t="n">
-        <v>35.95116913062397</v>
+        <v>36.23286340434844</v>
       </c>
       <c r="D16" t="n">
-        <v>1.31830129806033</v>
+        <v>1.339377021419528</v>
       </c>
       <c r="E16" t="n">
-        <v>11.67781125003279</v>
+        <v>11.66851778217176</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570823826618281</v>
+        <v>0.7569871326127755</v>
       </c>
       <c r="G16" t="n">
-        <v>22.22927471012016</v>
+        <v>22.49954967653368</v>
       </c>
       <c r="H16" t="n">
-        <v>36.82625861969909</v>
+        <v>36.7739918764894</v>
       </c>
       <c r="I16" t="n">
-        <v>2.079612422347736</v>
+        <v>2.08728060033456</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731764891636426</v>
+        <v>4.731169578829848</v>
       </c>
       <c r="K16" t="n">
-        <v>20.37989442544165</v>
+        <v>20.14312633160844</v>
       </c>
       <c r="L16" t="n">
-        <v>43.59967633045118</v>
+        <v>43.55449480999704</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9307398865168</v>
+        <v>99.93048454595392</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.63333632174913</v>
+        <v>81.63331668679504</v>
       </c>
       <c r="C17" t="n">
-        <v>37.39644920054057</v>
+        <v>37.51650880529559</v>
       </c>
       <c r="D17" t="n">
-        <v>1.319419575697568</v>
+        <v>1.340521097295705</v>
       </c>
       <c r="E17" t="n">
-        <v>12.56842482098519</v>
+        <v>12.47938310922628</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577245941952035</v>
+        <v>0.7576337397317181</v>
       </c>
       <c r="G17" t="n">
-        <v>22.78260255789562</v>
+        <v>22.97101690134072</v>
       </c>
       <c r="H17" t="n">
-        <v>37.39196867532129</v>
+        <v>37.25765211693407</v>
       </c>
       <c r="I17" t="n">
-        <v>2.077417383934236</v>
+        <v>2.09189884894331</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735778713720022</v>
+        <v>4.735210873323239</v>
       </c>
       <c r="K17" t="n">
-        <v>18.36666367825088</v>
+        <v>18.36668331320497</v>
       </c>
       <c r="L17" t="n">
-        <v>44.16769856576853</v>
+        <v>44.04713743132748</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93081144455999</v>
+        <v>99.93032954982803</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.31059979331751</v>
+        <v>79.22530555277254</v>
       </c>
       <c r="C18" t="n">
-        <v>35.39396521255505</v>
+        <v>35.43108522036961</v>
       </c>
       <c r="D18" t="n">
-        <v>1.236746296393004</v>
+        <v>1.253701874755125</v>
       </c>
       <c r="E18" t="n">
-        <v>12.06964237738897</v>
+        <v>11.96190714620933</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582763126560687</v>
+        <v>0.7581898388636437</v>
       </c>
       <c r="G18" t="n">
-        <v>21.35507146828148</v>
+        <v>21.48329258848644</v>
       </c>
       <c r="H18" t="n">
-        <v>37.41919471439182</v>
+        <v>37.28499903525788</v>
       </c>
       <c r="I18" t="n">
-        <v>1.732441670105729</v>
+        <v>1.744528576302362</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739226954100429</v>
+        <v>4.738686492897774</v>
       </c>
       <c r="K18" t="n">
-        <v>20.6894002066825</v>
+        <v>20.77469444722746</v>
       </c>
       <c r="L18" t="n">
-        <v>43.85892854231984</v>
+        <v>43.7361120310434</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94229396155738</v>
+        <v>99.94189169864046</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.4932653771009</v>
+        <v>78.26609877581525</v>
       </c>
       <c r="C19" t="n">
-        <v>34.84301893712873</v>
+        <v>34.74018030695478</v>
       </c>
       <c r="D19" t="n">
-        <v>1.20832401601621</v>
+        <v>1.219800138852687</v>
       </c>
       <c r="E19" t="n">
-        <v>12.03302844508041</v>
+        <v>11.88088730388763</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587414889308692</v>
+        <v>0.758659569450596</v>
       </c>
       <c r="G19" t="n">
-        <v>20.86429997334498</v>
+        <v>20.90235630186573</v>
       </c>
       <c r="H19" t="n">
-        <v>37.44215009531663</v>
+        <v>37.30809866490684</v>
       </c>
       <c r="I19" t="n">
-        <v>1.44458705259388</v>
+        <v>1.454674487785545</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742134305817933</v>
+        <v>4.741622309066226</v>
       </c>
       <c r="K19" t="n">
-        <v>21.50673462289909</v>
+        <v>21.73390122418476</v>
       </c>
       <c r="L19" t="n">
-        <v>43.60212306024702</v>
+        <v>43.47745934174095</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95187662027485</v>
+        <v>99.9515408728805</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.04504185711248</v>
+        <v>75.70026188085802</v>
       </c>
       <c r="C20" t="n">
-        <v>32.61680749402207</v>
+        <v>32.39790454240298</v>
       </c>
       <c r="D20" t="n">
-        <v>1.122178424861957</v>
+        <v>1.128357496231514</v>
       </c>
       <c r="E20" t="n">
-        <v>11.37589531871113</v>
+        <v>11.19237944529104</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7591420727247178</v>
+        <v>0.7590647464289154</v>
       </c>
       <c r="G20" t="n">
-        <v>19.37681198883127</v>
+        <v>19.33540558889917</v>
       </c>
       <c r="H20" t="n">
-        <v>37.46191798563743</v>
+        <v>37.3280237845423</v>
       </c>
       <c r="I20" t="n">
-        <v>1.204458111816491</v>
+        <v>1.212876154284389</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744637954529486</v>
+        <v>4.744154665180722</v>
       </c>
       <c r="K20" t="n">
-        <v>23.95495814288753</v>
+        <v>24.29973811914197</v>
       </c>
       <c r="L20" t="n">
-        <v>43.38810694496279</v>
+        <v>43.26194971379434</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95987258187239</v>
+        <v>99.95959237533928</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.16453055208596</v>
+        <v>81.61449658330463</v>
       </c>
       <c r="C21" t="n">
-        <v>36.44405251318445</v>
+        <v>36.05475620676822</v>
       </c>
       <c r="D21" t="n">
-        <v>1.122949972689498</v>
+        <v>1.12916712655277</v>
       </c>
       <c r="E21" t="n">
-        <v>13.43126835901234</v>
+        <v>13.16789263902776</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7596640168327393</v>
+        <v>0.7596093981342104</v>
       </c>
       <c r="G21" t="n">
-        <v>21.15522707977171</v>
+        <v>21.02395741121956</v>
       </c>
       <c r="H21" t="n">
-        <v>39.25276739533996</v>
+        <v>39.02948584967014</v>
       </c>
       <c r="I21" t="n">
-        <v>1.694753623235087</v>
+        <v>1.756825420361384</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747900105204621</v>
+        <v>4.747558738338816</v>
       </c>
       <c r="K21" t="n">
-        <v>17.83546944791406</v>
+        <v>18.38550341669538</v>
       </c>
       <c r="L21" t="n">
-        <v>45.66402506540302</v>
+        <v>45.50122151822573</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94354702650151</v>
+        <v>99.94148114168931</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_4_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_4_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.22237901379605</v>
+        <v>43.65117406602363</v>
       </c>
       <c r="M2" t="n">
-        <v>100.2536890897408</v>
+        <v>96.4938745223487</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.0531431906804</v>
+        <v>81.5734552154926</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92117761219669</v>
+        <v>43.32901077104816</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228802560603981</v>
+        <v>2.184888011205653</v>
       </c>
       <c r="E3" t="n">
-        <v>5.703546093199088</v>
+        <v>4.167874721539389</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429341868679938</v>
+        <v>0.7377010504649498</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97023309600151</v>
+        <v>32.86435716855169</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17497259592771</v>
+        <v>33.93424832138768</v>
       </c>
       <c r="I3" t="n">
-        <v>6.589315990155143</v>
+        <v>3.073754376937291</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643338667924962</v>
+        <v>4.610631565405936</v>
       </c>
       <c r="K3" t="n">
-        <v>11.9468568093196</v>
+        <v>18.42654478450739</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89545055982295</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7634849813392</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.05966213297815</v>
+        <v>88.75187104086153</v>
       </c>
       <c r="C4" t="n">
-        <v>42.56721765538074</v>
+        <v>42.92826257428744</v>
       </c>
       <c r="D4" t="n">
-        <v>2.180543635768847</v>
+        <v>2.190683578681293</v>
       </c>
       <c r="E4" t="n">
-        <v>6.49716156597137</v>
+        <v>6.558850410371163</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444994423491016</v>
+        <v>0.7396578538310228</v>
       </c>
       <c r="G4" t="n">
-        <v>33.23469601676931</v>
+        <v>33.55294093485845</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24697434805867</v>
+        <v>34.02426127622704</v>
       </c>
       <c r="I4" t="n">
-        <v>5.502665609378965</v>
+        <v>7.062615400448683</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653121514681885</v>
+        <v>4.622861586443892</v>
       </c>
       <c r="K4" t="n">
-        <v>12.94033786702187</v>
+        <v>11.24812895913845</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30940792231529</v>
+        <v>45.58881077045215</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81696344471789</v>
+        <v>99.76520230387804</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.90743664267765</v>
+        <v>87.81536290587546</v>
       </c>
       <c r="C5" t="n">
-        <v>42.26893428297191</v>
+        <v>43.08654344837368</v>
       </c>
       <c r="D5" t="n">
-        <v>2.124377527451109</v>
+        <v>2.146981861029674</v>
       </c>
       <c r="E5" t="n">
-        <v>7.095430028747302</v>
+        <v>7.411123721628595</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458264629024519</v>
+        <v>0.7413139850699317</v>
       </c>
       <c r="G5" t="n">
-        <v>32.37864181736467</v>
+        <v>32.88359682446927</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30801729351279</v>
+        <v>34.10044331321685</v>
       </c>
       <c r="I5" t="n">
-        <v>4.593728119559004</v>
+        <v>5.898690793774065</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661415393140325</v>
+        <v>4.633212406687073</v>
       </c>
       <c r="K5" t="n">
-        <v>14.09256335732234</v>
+        <v>12.18463709412456</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48565053722303</v>
+        <v>44.53263569637817</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84714817751728</v>
+        <v>99.80381623887641</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.43542984595204</v>
+        <v>86.65570773878214</v>
       </c>
       <c r="C6" t="n">
-        <v>41.51028683412312</v>
+        <v>42.84262383535056</v>
       </c>
       <c r="D6" t="n">
-        <v>2.052305656011632</v>
+        <v>2.092275004966841</v>
       </c>
       <c r="E6" t="n">
-        <v>7.493693131892337</v>
+        <v>8.04309686356415</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469553036656649</v>
+        <v>0.7427183504379741</v>
       </c>
       <c r="G6" t="n">
-        <v>31.28016036560224</v>
+        <v>32.04569584777367</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35994396862058</v>
+        <v>34.1650441201468</v>
       </c>
       <c r="I6" t="n">
-        <v>3.833900772249177</v>
+        <v>4.924887861655376</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668470647910405</v>
+        <v>4.641989690237337</v>
       </c>
       <c r="K6" t="n">
-        <v>15.56457015404795</v>
+        <v>13.34429226121786</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79753945295229</v>
+        <v>43.64923138138231</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87239644112336</v>
+        <v>99.83614747795072</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.77142891575048</v>
+        <v>85.29755368682076</v>
       </c>
       <c r="C7" t="n">
-        <v>40.44159974533824</v>
+        <v>42.24964421778895</v>
       </c>
       <c r="D7" t="n">
-        <v>1.971193584638768</v>
+        <v>2.028160352324998</v>
       </c>
       <c r="E7" t="n">
-        <v>7.730696518817439</v>
+        <v>8.481739136278499</v>
       </c>
       <c r="F7" t="n">
-        <v>0.74791760629362</v>
+        <v>0.7439114550258574</v>
       </c>
       <c r="G7" t="n">
-        <v>30.04389295450908</v>
+        <v>31.06370320671608</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40420988950653</v>
+        <v>34.21992693118943</v>
       </c>
       <c r="I7" t="n">
-        <v>3.199033322649924</v>
+        <v>4.110666011374295</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674485039335125</v>
+        <v>4.649446593911608</v>
       </c>
       <c r="K7" t="n">
-        <v>17.22857108424953</v>
+        <v>14.70244631317923</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22333192673864</v>
+        <v>42.91110702843028</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8935027563264</v>
+        <v>99.86319755939846</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.5661817519518</v>
+        <v>83.751267764738</v>
       </c>
       <c r="C8" t="n">
-        <v>42.73866482417882</v>
+        <v>41.34215406317576</v>
       </c>
       <c r="D8" t="n">
-        <v>1.975376997691951</v>
+        <v>1.955391035298172</v>
       </c>
       <c r="E8" t="n">
-        <v>9.556654631610597</v>
+        <v>8.749124126571628</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495048924441314</v>
+        <v>0.7449270769375033</v>
       </c>
       <c r="G8" t="n">
-        <v>30.54783146304223</v>
+        <v>29.94915402223694</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47722505243005</v>
+        <v>34.26664553912514</v>
       </c>
       <c r="I8" t="n">
-        <v>5.57518313695702</v>
+        <v>3.430231733709225</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684405577775822</v>
+        <v>4.655794230859394</v>
       </c>
       <c r="K8" t="n">
-        <v>12.43381824804819</v>
+        <v>16.248732235262</v>
       </c>
       <c r="L8" t="n">
-        <v>44.64207105683973</v>
+        <v>42.29492853457962</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81455412906675</v>
+        <v>99.88581483301738</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.44574003542776</v>
+        <v>82.06323552835833</v>
       </c>
       <c r="C9" t="n">
-        <v>41.48325725950889</v>
+        <v>40.18698509879082</v>
       </c>
       <c r="D9" t="n">
-        <v>1.879242028053421</v>
+        <v>1.876377455028723</v>
       </c>
       <c r="E9" t="n">
-        <v>9.867301296610526</v>
+        <v>8.872563788634926</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508657997492119</v>
+        <v>0.7457930225966375</v>
       </c>
       <c r="G9" t="n">
-        <v>29.06117101612309</v>
+        <v>28.73896647272857</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53982678846375</v>
+        <v>34.30647903944531</v>
       </c>
       <c r="I9" t="n">
-        <v>4.654421857995183</v>
+        <v>2.861849358695163</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692911248432575</v>
+        <v>4.661206391228983</v>
       </c>
       <c r="K9" t="n">
-        <v>14.55425996457225</v>
+        <v>17.9367644716417</v>
       </c>
       <c r="L9" t="n">
-        <v>43.80761657767005</v>
+        <v>41.78096621474222</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84513380175119</v>
+        <v>99.90471578517473</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.15480227376193</v>
+        <v>86.45674133253004</v>
       </c>
       <c r="C10" t="n">
-        <v>39.91408985914754</v>
+        <v>43.28358937027184</v>
       </c>
       <c r="D10" t="n">
-        <v>1.776503834668762</v>
+        <v>1.878420926629448</v>
       </c>
       <c r="E10" t="n">
-        <v>9.975309913390872</v>
+        <v>10.64422112584859</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520350675755333</v>
+        <v>0.7466052295742958</v>
       </c>
       <c r="G10" t="n">
-        <v>27.47239630628343</v>
+        <v>30.06148014427456</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59361310847454</v>
+        <v>35.6350560186623</v>
       </c>
       <c r="I10" t="n">
-        <v>3.884724871021712</v>
+        <v>2.824675202701498</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700219172347084</v>
+        <v>4.666282684839347</v>
       </c>
       <c r="K10" t="n">
-        <v>16.84519772623807</v>
+        <v>13.54325866746996</v>
       </c>
       <c r="L10" t="n">
-        <v>43.11142291855897</v>
+        <v>43.07909855117251</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87071050394459</v>
+        <v>99.9059465889143</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.73835518246813</v>
+        <v>86.28805744198634</v>
       </c>
       <c r="C11" t="n">
-        <v>38.09934315160002</v>
+        <v>43.44573787932977</v>
       </c>
       <c r="D11" t="n">
-        <v>1.66929157494488</v>
+        <v>1.864079722718935</v>
       </c>
       <c r="E11" t="n">
-        <v>9.913565740691761</v>
+        <v>11.00505951882159</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530415282137797</v>
+        <v>0.7473045015382661</v>
       </c>
       <c r="G11" t="n">
-        <v>25.81443327206578</v>
+        <v>29.86998550198162</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63991029783387</v>
+        <v>35.70644800284872</v>
       </c>
       <c r="I11" t="n">
-        <v>3.241603217381936</v>
+        <v>2.424527059463051</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706509551336124</v>
+        <v>4.670653134614161</v>
       </c>
       <c r="K11" t="n">
-        <v>19.26164481753187</v>
+        <v>13.71194255801365</v>
       </c>
       <c r="L11" t="n">
-        <v>42.53110300667304</v>
+        <v>42.76157761707691</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89209097580493</v>
+        <v>99.91925805442033</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.35235094684666</v>
+        <v>84.61438377326343</v>
       </c>
       <c r="C12" t="n">
-        <v>36.21455054937556</v>
+        <v>42.14949544570736</v>
       </c>
       <c r="D12" t="n">
-        <v>1.5645862866204</v>
+        <v>1.792508673903485</v>
       </c>
       <c r="E12" t="n">
-        <v>9.742484092938664</v>
+        <v>10.91953009091603</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539079385773378</v>
+        <v>0.7478997849041422</v>
       </c>
       <c r="G12" t="n">
-        <v>24.19523880702815</v>
+        <v>28.72313208985348</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67976517455755</v>
+        <v>35.73489083238724</v>
       </c>
       <c r="I12" t="n">
-        <v>2.704444031016192</v>
+        <v>2.022048645648181</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711924616108362</v>
+        <v>4.674373655650887</v>
       </c>
       <c r="K12" t="n">
-        <v>21.64764905315334</v>
+        <v>15.38561622673657</v>
       </c>
       <c r="L12" t="n">
-        <v>42.04775586365494</v>
+        <v>42.3975403536821</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90995546618385</v>
+        <v>99.93265202612602</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.92285169366713</v>
+        <v>85.7822413898043</v>
       </c>
       <c r="C13" t="n">
-        <v>34.20233509851506</v>
+        <v>43.1349156501491</v>
       </c>
       <c r="D13" t="n">
-        <v>1.458961887523358</v>
+        <v>1.793801595700032</v>
       </c>
       <c r="E13" t="n">
-        <v>9.460763361714333</v>
+        <v>11.55835710953486</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546546473199387</v>
+        <v>0.7484392388814722</v>
       </c>
       <c r="G13" t="n">
-        <v>22.56183093310256</v>
+        <v>29.06543056671132</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71411377671719</v>
+        <v>36.08224683328518</v>
       </c>
       <c r="I13" t="n">
-        <v>2.255935541540124</v>
+        <v>1.856220802682234</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716591545749618</v>
+        <v>4.6777452430092</v>
       </c>
       <c r="K13" t="n">
-        <v>24.07714830633287</v>
+        <v>14.21775861019569</v>
       </c>
       <c r="L13" t="n">
-        <v>41.64539314984607</v>
+        <v>42.58549630995939</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92487655469401</v>
+        <v>99.93817057030418</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.10232541161363</v>
+        <v>83.95780072614021</v>
       </c>
       <c r="C14" t="n">
-        <v>38.62874927602885</v>
+        <v>41.59939629198056</v>
       </c>
       <c r="D14" t="n">
-        <v>1.460717525193518</v>
+        <v>1.717702552097518</v>
       </c>
       <c r="E14" t="n">
-        <v>11.92106241408669</v>
+        <v>11.32597994150734</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555627588601556</v>
+        <v>0.7488991664349658</v>
       </c>
       <c r="G14" t="n">
-        <v>24.53789037431945</v>
+        <v>27.83237810799789</v>
       </c>
       <c r="H14" t="n">
-        <v>36.70479663320021</v>
+        <v>36.10441993518639</v>
       </c>
       <c r="I14" t="n">
-        <v>3.000028463077632</v>
+        <v>1.547801232697569</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722267242875973</v>
+        <v>4.680619790218534</v>
       </c>
       <c r="K14" t="n">
-        <v>16.89767458838638</v>
+        <v>16.04219927385979</v>
       </c>
       <c r="L14" t="n">
-        <v>44.37369537804322</v>
+        <v>42.30684274519624</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90011924245844</v>
+        <v>99.9484383110366</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.34469107329227</v>
+        <v>83.13714800268326</v>
       </c>
       <c r="C15" t="n">
-        <v>38.33426935401036</v>
+        <v>40.99068821778636</v>
       </c>
       <c r="D15" t="n">
-        <v>1.432982615995806</v>
+        <v>1.682710540045745</v>
       </c>
       <c r="E15" t="n">
-        <v>12.11180775915226</v>
+        <v>11.31495376824394</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563281748823597</v>
+        <v>0.7492949777006703</v>
       </c>
       <c r="G15" t="n">
-        <v>24.07198498898836</v>
+        <v>27.26539349882018</v>
       </c>
       <c r="H15" t="n">
-        <v>36.74198009560005</v>
+        <v>36.12350199161343</v>
       </c>
       <c r="I15" t="n">
-        <v>2.502556345658683</v>
+        <v>1.318199615630102</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727051093014749</v>
+        <v>4.683093610629188</v>
       </c>
       <c r="K15" t="n">
-        <v>17.65530892670773</v>
+        <v>16.86285199731674</v>
       </c>
       <c r="L15" t="n">
-        <v>43.92708759530754</v>
+        <v>42.10254300878426</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91666587602563</v>
+        <v>99.95608322388736</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.85687366839157</v>
+        <v>80.88449844285782</v>
       </c>
       <c r="C16" t="n">
-        <v>36.23286340434844</v>
+        <v>38.94278650493373</v>
       </c>
       <c r="D16" t="n">
-        <v>1.339377021419528</v>
+        <v>1.589285223374018</v>
       </c>
       <c r="E16" t="n">
-        <v>11.66851778217176</v>
+        <v>10.86990548094024</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569871326127755</v>
+        <v>0.7496343394232894</v>
       </c>
       <c r="G16" t="n">
-        <v>22.49954967653368</v>
+        <v>25.7515989624543</v>
       </c>
       <c r="H16" t="n">
-        <v>36.7739918764894</v>
+        <v>36.13986261623756</v>
       </c>
       <c r="I16" t="n">
-        <v>2.08728060033456</v>
+        <v>1.098997199032853</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731169578829848</v>
+        <v>4.685214621395557</v>
       </c>
       <c r="K16" t="n">
-        <v>20.14312633160844</v>
+        <v>19.11550155714218</v>
       </c>
       <c r="L16" t="n">
-        <v>43.55449480999704</v>
+        <v>41.90509528193436</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93048454595392</v>
+        <v>99.96338334401028</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.63331668679504</v>
+        <v>85.10875264721393</v>
       </c>
       <c r="C17" t="n">
-        <v>37.51650880529559</v>
+        <v>41.76838434071836</v>
       </c>
       <c r="D17" t="n">
-        <v>1.340521097295705</v>
+        <v>1.590013702909834</v>
       </c>
       <c r="E17" t="n">
-        <v>12.47938310922628</v>
+        <v>12.37703971624887</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576337397317181</v>
+        <v>0.7499779487814984</v>
       </c>
       <c r="G17" t="n">
-        <v>22.97101690134072</v>
+        <v>27.07049831735745</v>
       </c>
       <c r="H17" t="n">
-        <v>37.25765211693407</v>
+        <v>37.4635236321523</v>
       </c>
       <c r="I17" t="n">
-        <v>2.09189884894331</v>
+        <v>1.170337149879612</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735210873323239</v>
+        <v>4.687362179884363</v>
       </c>
       <c r="K17" t="n">
-        <v>18.36668331320497</v>
+        <v>14.89124735278605</v>
       </c>
       <c r="L17" t="n">
-        <v>44.04713743132748</v>
+        <v>43.30137494152721</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93032954982803</v>
+        <v>99.96100663503162</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.22530555277254</v>
+        <v>86.63603791575665</v>
       </c>
       <c r="C18" t="n">
-        <v>35.43108522036961</v>
+        <v>42.46913449960521</v>
       </c>
       <c r="D18" t="n">
-        <v>1.253701874755125</v>
+        <v>1.591208133819756</v>
       </c>
       <c r="E18" t="n">
-        <v>11.96190714620933</v>
+        <v>12.94955147271694</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581898388636437</v>
+        <v>0.7505413381674799</v>
       </c>
       <c r="G18" t="n">
-        <v>21.48329258848644</v>
+        <v>27.20973670571737</v>
       </c>
       <c r="H18" t="n">
-        <v>37.28499903525788</v>
+        <v>37.49166652836694</v>
       </c>
       <c r="I18" t="n">
-        <v>1.744528576302362</v>
+        <v>1.952450373421414</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738686492897774</v>
+        <v>4.690883363546748</v>
       </c>
       <c r="K18" t="n">
-        <v>20.77469444722746</v>
+        <v>13.36396208424337</v>
       </c>
       <c r="L18" t="n">
-        <v>43.7361120310434</v>
+        <v>44.10187059021222</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94189169864046</v>
+        <v>99.93496717406079</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.26609877581525</v>
+        <v>84.16702097939225</v>
       </c>
       <c r="C19" t="n">
-        <v>34.74018030695478</v>
+        <v>40.30319437703236</v>
       </c>
       <c r="D19" t="n">
-        <v>1.219800138852687</v>
+        <v>1.49807349277862</v>
       </c>
       <c r="E19" t="n">
-        <v>11.88088730388763</v>
+        <v>12.46295273535059</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758659569450596</v>
+        <v>0.7510252765862787</v>
       </c>
       <c r="G19" t="n">
-        <v>20.90235630186573</v>
+        <v>25.61712980090761</v>
       </c>
       <c r="H19" t="n">
-        <v>37.30809866490684</v>
+        <v>37.51584062364351</v>
       </c>
       <c r="I19" t="n">
-        <v>1.454674487785545</v>
+        <v>1.628091071461403</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741622309066226</v>
+        <v>4.69390797866424</v>
       </c>
       <c r="K19" t="n">
-        <v>21.73390122418476</v>
+        <v>15.83297902060776</v>
       </c>
       <c r="L19" t="n">
-        <v>43.47745934174095</v>
+        <v>43.80959186976487</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9515408728805</v>
+        <v>99.94576526740497</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.70026188085802</v>
+        <v>81.54339841456307</v>
       </c>
       <c r="C20" t="n">
-        <v>32.39790454240298</v>
+        <v>37.93168250071911</v>
       </c>
       <c r="D20" t="n">
-        <v>1.128357496231514</v>
+        <v>1.399542908022367</v>
       </c>
       <c r="E20" t="n">
-        <v>11.19237944529104</v>
+        <v>11.86949451317818</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590647464289154</v>
+        <v>0.7514420335556892</v>
       </c>
       <c r="G20" t="n">
-        <v>19.33540558889917</v>
+        <v>23.93225199536108</v>
       </c>
       <c r="H20" t="n">
-        <v>37.3280237845423</v>
+        <v>37.536658815162</v>
       </c>
       <c r="I20" t="n">
-        <v>1.212876154284389</v>
+        <v>1.357495439560693</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744154665180722</v>
+        <v>4.696512709723055</v>
       </c>
       <c r="K20" t="n">
-        <v>24.29973811914197</v>
+        <v>18.45660158543693</v>
       </c>
       <c r="L20" t="n">
-        <v>43.26194971379434</v>
+        <v>43.56649116185893</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95959237533928</v>
+        <v>99.95477524801497</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.61449658330463</v>
+        <v>78.93402100892253</v>
       </c>
       <c r="C21" t="n">
-        <v>36.05475620676822</v>
+        <v>35.53189507774908</v>
       </c>
       <c r="D21" t="n">
-        <v>1.12916712655277</v>
+        <v>1.301997985629403</v>
       </c>
       <c r="E21" t="n">
-        <v>13.16789263902776</v>
+        <v>11.23084918568885</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7596093981342104</v>
+        <v>0.7518011825511712</v>
       </c>
       <c r="G21" t="n">
-        <v>21.02395741121956</v>
+        <v>22.26422906430633</v>
       </c>
       <c r="H21" t="n">
-        <v>39.02948584967014</v>
+        <v>37.55459932514842</v>
       </c>
       <c r="I21" t="n">
-        <v>1.756825420361384</v>
+        <v>1.131786874653538</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747558738338816</v>
+        <v>4.698757390944817</v>
       </c>
       <c r="K21" t="n">
-        <v>18.38550341669538</v>
+        <v>21.06597899107749</v>
       </c>
       <c r="L21" t="n">
-        <v>45.50122151822573</v>
+        <v>43.36441772451897</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94148114168931</v>
+        <v>99.96229179334554</v>
       </c>
     </row>
   </sheetData>
